--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488221_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488221_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.981</v>
+        <v>1.0652</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8497</v>
+        <v>1.0571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1313</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0.6502</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1455</v>
+        <v>0.2298</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6056</v>
+        <v>-0.3982</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7511</v>
+        <v>0.628</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0699</v>
+        <v>0.35</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4798</v>
+        <v>1.883</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4099</v>
+        <v>-1.533</v>
       </c>
       <c r="G3" t="n">
         <v>-0.09030000000000001</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3221</v>
+        <v>-0.042</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9302</v>
+        <v>-0.5269</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6081</v>
+        <v>0.485</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.417</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8205</v>
+        <v>-0.57</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0791</v>
+        <v>0.153</v>
       </c>
       <c r="G4" t="n">
         <v>0.544</v>
@@ -766,13 +766,13 @@
         <v>0.1853</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2119</v>
+        <v>0.1125</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2736</v>
+        <v>-0.023</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0617</v>
+        <v>0.1355</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2589</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9307</v>
+        <v>-0.8327</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0235</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>-0.9071</v>
@@ -844,10 +844,10 @@
         <v>0.1853</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0336</v>
+        <v>0.1315</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U5" t="n">
         <v>0.143</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1454</v>
+        <v>-1.827</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.4804</v>
+        <v>-3.1866</v>
       </c>
       <c r="F6" t="n">
-        <v>1.335</v>
+        <v>1.3596</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1995</v>
@@ -922,13 +922,13 @@
         <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.5158</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8754</v>
+        <v>-0.5816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0413</v>
+        <v>0.0659</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5781</v>
+        <v>-2.3811</v>
       </c>
       <c r="E7" t="n">
         <v>-3.1351</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7135</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3823</v>
+        <v>-0.1853</v>
       </c>
       <c r="T7" t="n">
         <v>-0.383</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007</v>
+        <v>0.1977</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6693</v>
+        <v>-2.8568</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0095</v>
+        <v>-4.6708</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6597</v>
+        <v>1.8139</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2913</v>
+        <v>-1.0225</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4189</v>
+        <v>-1.2726</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1275</v>
+        <v>0.2501</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8021</v>
+        <v>-1.165</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.885</v>
+        <v>-0.524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0829</v>
+        <v>-0.6409</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5107</v>
+        <v>0.1425</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0446</v>
+        <v>0.891</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0095</v>
+        <v>-0.0376</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6454</v>
+        <v>-0.7265</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3641</v>
+        <v>0.6889</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8316</v>
+        <v>-0.3144</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8316</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3843</v>
+        <v>-3.086</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8781</v>
+        <v>-3.4922</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4939</v>
+        <v>0.4062</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0225</v>
+        <v>-3.1897</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2726</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2501</v>
+        <v>-4.0753</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.165</v>
+        <v>-2.0936</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.524</v>
+        <v>1.1293</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6409</v>
+        <v>-3.2228</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1425</v>
+        <v>-1.0961</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.2437</v>
       </c>
       <c r="O9" t="n">
-        <v>0.891</v>
+        <v>-0.8524</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5083</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9339</v>
+        <v>-0.4722</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3688</v>
+        <v>-0.0361</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.429</v>
+        <v>-3.3427</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.786</v>
+        <v>-2.7814</v>
       </c>
       <c r="F10" t="n">
-        <v>0.357</v>
+        <v>-0.5613</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1897</v>
+        <v>-0.2913</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8856000000000001</v>
+        <v>-1.4189</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0753</v>
+        <v>1.1275</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0936</v>
+        <v>-0.8021</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1293</v>
+        <v>-0.885</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.2228</v>
+        <v>0.0829</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0961</v>
+        <v>0.5107</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2437</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8524</v>
+        <v>1.0446</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.3361</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.766</v>
+        <v>-0.1265</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0853</v>
+        <v>0.4626</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>-2.8316</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>-2.8316</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9126</v>
+        <v>-5.4279</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3075</v>
+        <v>-3.6012</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6051</v>
+        <v>-1.8267</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4573</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6357</v>
+        <v>0.1203</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0621</v>
+        <v>-0.3559</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6979</v>
+        <v>0.4763</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2027</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7321</v>
+        <v>-6.1687</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2842</v>
+        <v>-6.4253</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5521</v>
+        <v>0.2566</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0795</v>
@@ -1390,13 +1390,13 @@
         <v>2.7793</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2917</v>
+        <v>-0.1449</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4999</v>
+        <v>-0.641</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7916</v>
+        <v>0.4961</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9444</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.472</v>
+        <v>-24.9247</v>
       </c>
       <c r="E13" t="n">
-        <v>-25.3953</v>
+        <v>-24.8481</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07640000000000025</v>
+        <v>-0.07659999999999995</v>
       </c>
       <c r="G13" t="n">
         <v>-13.7401</v>
@@ -1444,7 +1444,7 @@
         <v>-7.6661</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8578</v>
+        <v>2.857800000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-10.5237</v>
@@ -1456,10 +1456,10 @@
         <v>-6.267</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1929000000000001</v>
+        <v>0.1928999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.926499999999999</v>
+        <v>-0.9264999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.8229</v>
@@ -1468,13 +1468,13 @@
         <v>13.8966</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0508</v>
+        <v>-0.5036999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7937</v>
+        <v>-4.2463</v>
       </c>
       <c r="U13" t="n">
-        <v>3.742999999999999</v>
+        <v>3.742900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-9.7547</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9157</v>
+        <v>7.8408</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4236</v>
+        <v>4.6194</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4922</v>
+        <v>3.2213</v>
       </c>
       <c r="G14" t="n">
         <v>4.2116</v>
@@ -1546,13 +1546,13 @@
         <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3156</v>
+        <v>0.2406</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4166</v>
+        <v>-0.2207</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7322</v>
+        <v>0.4613</v>
       </c>
       <c r="V14" t="n">
         <v>2.8327</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0298</v>
+        <v>6.4405</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0428</v>
+        <v>2.7491</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9869</v>
+        <v>3.6915</v>
       </c>
       <c r="G15" t="n">
         <v>3.4856</v>
@@ -1624,13 +1624,13 @@
         <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0826</v>
+        <v>0.4934</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1679</v>
+        <v>-0.4616</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2505</v>
+        <v>0.955</v>
       </c>
       <c r="V15" t="n">
         <v>2.8321</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0616</v>
+        <v>4.3073</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6593</v>
+        <v>2.7572</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4024</v>
+        <v>1.5501</v>
       </c>
       <c r="G16" t="n">
         <v>3.2556</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3057</v>
+        <v>-0.06</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2962</v>
+        <v>0.4439</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3317</v>
+        <v>3.6255</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0866</v>
+        <v>1.3804</v>
       </c>
       <c r="F17" t="n">
         <v>2.245</v>
@@ -1780,10 +1780,10 @@
         <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1729</v>
+        <v>0.1209</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7113</v>
+        <v>-0.4175</v>
       </c>
       <c r="U17" t="n">
         <v>0.5384</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7165</v>
+        <v>2.228</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6588</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0578</v>
+        <v>1.2547</v>
       </c>
       <c r="G18" t="n">
         <v>2.6487</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8265</v>
+        <v>0.3379</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8133</v>
+        <v>0.1278</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0132</v>
+        <v>0.2101</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9439</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8983</v>
+        <v>2.1916</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3716</v>
+        <v>-0.9799</v>
       </c>
       <c r="F19" t="n">
-        <v>3.27</v>
+        <v>3.1715</v>
       </c>
       <c r="G19" t="n">
         <v>0.06510000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2049</v>
+        <v>0.0883</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6354</v>
+        <v>-0.2437</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4305</v>
+        <v>0.332</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8632</v>
+        <v>2.1821</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.721</v>
       </c>
       <c r="F20" t="n">
-        <v>2.78</v>
+        <v>2.9031</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7853</v>
@@ -2014,13 +2014,13 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1455</v>
+        <v>0.1735</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.526</v>
+        <v>-0.3301</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3805</v>
+        <v>0.5036</v>
       </c>
       <c r="V20" t="n">
         <v>4.091</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.613</v>
+        <v>1.637</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3281</v>
+        <v>-1.2302</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9411</v>
+        <v>2.8672</v>
       </c>
       <c r="G21" t="n">
         <v>3.3258</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1091</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.766</v>
+        <v>-0.6681</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8511</v>
+        <v>0.7772</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3155</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. REMESAL LEÓN</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3221</v>
+        <v>0.4574</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3221</v>
+        <v>0.233</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.2245</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3221</v>
+        <v>-0.7762</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3221</v>
+        <v>-1.0144</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.2381</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3221</v>
+        <v>-0.6314</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3221</v>
+        <v>-0.6314</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-0.1448</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.2381</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-0.3958</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.3945</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0.0012</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>J. REMESAL LEÓN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2364</v>
+        <v>0.3221</v>
       </c>
       <c r="E24" t="n">
-        <v>0.135</v>
+        <v>0.3221</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1014</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7762</v>
+        <v>0.3221</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0144</v>
+        <v>0.3221</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2381</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6314</v>
+        <v>0.3221</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6314</v>
+        <v>0.3221</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1448</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2381</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6168</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4924</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1244</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0624</v>
+        <v>-0.0126</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2146</v>
+        <v>-2.0187</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2769</v>
+        <v>2.0061</v>
       </c>
       <c r="G25" t="n">
         <v>-0.993</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3703</v>
+        <v>0.2953</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3071</v>
+        <v>-0.1113</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6775</v>
+        <v>0.4066</v>
       </c>
       <c r="V25" t="n">
         <v>0.3144</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2684</v>
+        <v>-1.7323</v>
       </c>
       <c r="E26" t="n">
-        <v>-2</v>
+        <v>-2.6855</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7316</v>
+        <v>0.9532</v>
       </c>
       <c r="G26" t="n">
         <v>-1.1163</v>
@@ -2482,13 +2482,13 @@
         <v>0.9264</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4599</v>
+        <v>-0.004</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3198</v>
+        <v>-0.0982</v>
       </c>
       <c r="V26" t="n">
         <v>0.3144</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.6324</v>
+        <v>-4.3375</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.7426</v>
+        <v>-5.6447</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1102</v>
+        <v>1.3072</v>
       </c>
       <c r="G27" t="n">
         <v>-2.5628</v>
@@ -2560,13 +2560,13 @@
         <v>0.7411</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6434</v>
+        <v>-0.3485</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7113</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0679</v>
+        <v>0.2649</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3144</v>
@@ -2596,10 +2596,10 @@
         <v>25.472</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07660000000000089</v>
+        <v>0.0766</v>
       </c>
       <c r="F28" t="n">
-        <v>25.3955</v>
+        <v>25.3954</v>
       </c>
       <c r="G28" t="n">
         <v>13.7402</v>
@@ -2641,10 +2641,10 @@
         <v>1.0507</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.7429</v>
+        <v>-3.7428</v>
       </c>
       <c r="U28" t="n">
-        <v>4.7938</v>
+        <v>4.793600000000001</v>
       </c>
       <c r="V28" t="n">
         <v>9.7547</v>
